--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -54,27 +54,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="008fb4ff"/>
+      <color rgb="004F95FF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ff9b9b"/>
+      <color rgb="00FF6363"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007fdce8"/>
+      <color rgb="003BC7D4"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00d7a8ff"/>
+      <color rgb="00A88BFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="008fe6ad"/>
+      <color rgb="00C98BFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00f0b0e0"/>
+      <color rgb="00FF7AC4"/>
     </font>
   </fonts>
   <fills count="12">
@@ -106,32 +106,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001e3163"/>
+        <fgColor rgb="0066FF1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005c1f1f"/>
+        <fgColor rgb="FF42421F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123f47"/>
+        <fgColor rgb="00BBCC1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003a2154"/>
+        <fgColor rgb="7C5CFF1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017402a"/>
+        <fgColor rgb="A34DFF1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004a2043"/>
+        <fgColor rgb="FF47AD1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -611,7 +611,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원본 증강표와 같은 배치입니다. 칸마다 선택지가 3개이고, 게임에서는 처치한 기물의 칸 하나를 그대로 펼쳐 그중 1개만 고릅니다.</t>
+          <t>원본 증강표와 같은 배치입니다. 칸마다 선택지가 3개이고, 게임에서는 처치를 해낸 기물의 칸 하나를 그대로 펼쳐 그중 1개만 고릅니다.</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>처치 카운트가 1·3·6·11 에 닿으면, 방금 처치한 기물의 칸(기물×티어)에 있는 선택지 3개를 그대로 펼쳐 보여주고 그중 1개만 고릅니다. 원본 증강표가 칸마다 3개씩 두고 있는 구조를 그대로 따랐습니다.</t>
+          <t>처치 카운트가 1·3·6·11 에 닿으면, 그 처치를 해낸 기물의 칸(기물×티어)에 있는 선택지 3개를 그대로 펼쳐 보여주고 그중 1개만 고릅니다. 원본 증강표가 칸마다 3개씩 두고 있는 구조를 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>#8fb4ff</t>
+          <t>#4F95FF</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>#1e3163</t>
+          <t>#0066FF1F</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>#ff9b9b</t>
+          <t>#FF6363</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>#5c1f1f</t>
+          <t>#FF42421F</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>#7fdce8</t>
+          <t>#3BC7D4</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>#123f47</t>
+          <t>#00BBCC1F</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>#d7a8ff</t>
+          <t>#A88BFF</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>#3a2154</t>
+          <t>#7C5CFF1F</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>#8fe6ad</t>
+          <t>#C98BFF</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>#17402a</t>
+          <t>#A34DFF1F</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>#f0b0e0</t>
+          <t>#FF7AC4</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>#4a2043</t>
+          <t>#FF47AD1F</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어 색상" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구현 목록'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구현 목록'!$A$1:$J$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -211,13 +211,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1258,7 +1258,7 @@
       </c>
     </row>
     <row r="22" ht="118" customHeight="1">
-      <c r="A22" s="6" t="n"/>
+      <c r="A22" s="7" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t>[K1c] 자신의 모든 제거를 처치로 간주합니다.
@@ -1292,23 +1292,18 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="118" customHeight="1">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[K1d] 이후 모든 강화에 필요한 처치 기물 수가 1 줄어듭니다. (1·3·6·11 → 0·2·5·10)
-▸ 발동 시점: 획득 즉시
-▸ 잠금 조건: 더 받을 강화가 없습니다</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>범례</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>범례</t>
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>자동 — 조건이 맞으면 알아서 발동</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1311,13 @@
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>자동 — 조건이 맞으면 알아서 발동</t>
+          <t>대상 지정 — 플레이어가 칸/기물을 고름</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
       <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>대상 지정 — 플레이어가 칸/기물을 고름</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>잠금 조건 있음 — 못 쓰는 상황이면 드래프트에서 ✕ 처리</t>
         </is>
@@ -1341,8 +1328,8 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A14:A16"/>
   </mergeCells>
@@ -1356,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1424,3113 +1411,3075 @@
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
     </row>
     <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>P1a</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>#지정불가</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>P1b</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr"/>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>P1c</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr"/>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>#포영</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>P3a</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr"/>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>P3b</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>폰이 뒤로도 움직일 수 있습니다. (뒤로는 처치할 수 없습니다.)</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>P3c</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>P6a</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>폰이 좌우로 움직일 수 있습니다. (좌우로는 처치할 수 없으며, 앙파상 대상이 되지 않습니다.)</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>P6b</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>폰이 정면에 있는 적 기물도 처치할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>P6c</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>#교환 #변이</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>P11a</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P11b</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 효과 만료</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>P11c</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr"/>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>R1a</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>룩이 기물을 최대 하나까지 통과할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>R1b</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>R1c</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>#지정불가</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>R3a</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>R3b</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>#포영</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>R3c</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>룩이 제거, 포영, 교환, 지정불가 효과에 면역이 됩니다.</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>#지정불가 #포영 #제거 #교환</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>R6a</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>상대에게 룩이 없습니다</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>R6b</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>상대에게 룩이 없습니다</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>R6c</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>지정한 아군 룩과 상대 폰의 위치를 교환합니다.</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>#교환</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>R11a</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>룩이 기물을 최대 두 개까지 통과할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr"/>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>R11b</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>R11c</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr"/>
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>아군 룩이 없습니다</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>N1a</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 지정한 아군 나이트가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>#지정불가</t>
         </is>
       </c>
     </row>
     <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>N1b</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>#교환</t>
         </is>
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>N1c</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr"/>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>처치했을 때</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr"/>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>N3a</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr"/>
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 수동 발동 가능 판정 / 수동 발동</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr"/>
+      <c r="J30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>N3b</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr"/>
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr"/>
+      <c r="J31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>N3c</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr"/>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>#변이</t>
         </is>
       </c>
     </row>
     <row r="33" ht="56" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>N6a</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>이동 직후</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>#포영</t>
         </is>
       </c>
     </row>
     <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>N6b</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>내 턴 시작</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr"/>
+      <c r="J34" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>N6c</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr"/>
+      <c r="J35" s="12" t="inlineStr"/>
     </row>
     <row r="36" ht="56" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>N11a</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C36" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>나이트를 2회 이상 강화해야 합니다</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>#지정불가</t>
         </is>
       </c>
     </row>
     <row r="37" ht="56" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>N11b</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>나이트의 움직임 범위가 2배로 늘어나며 대각선으로 먼저 이동할 수 있습니다. (직선으로 두 칸 + 대각선으로 두 칸. 도약이므로 경로는 무시합니다.)</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr"/>
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr"/>
+      <c r="J37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="56" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>N11c</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="39" ht="56" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>B1a</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 내 턴 시작</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>#교환 #비밀</t>
         </is>
       </c>
     </row>
     <row r="40" ht="56" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>B1b</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 상대가 둔 직후</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr"/>
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
     <row r="41" ht="56" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>B1c</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 예약 발동</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>상대 폰이 없습니다</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
     <row r="42" ht="56" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>B3a</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>처치했을 때 / 예약 발동</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>#비밀</t>
         </is>
       </c>
     </row>
     <row r="43" ht="56" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>B3b</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>처치했을 때 / 예약 발동</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>#비밀</t>
         </is>
       </c>
     </row>
     <row r="44" ht="56" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>B3c</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>처치했을 때 / 예약 발동</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>#비밀</t>
         </is>
       </c>
     </row>
     <row r="45" ht="56" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>B6a</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr"/>
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>#비밀</t>
         </is>
       </c>
     </row>
     <row r="46" ht="56" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>B6b</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C46" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 예약 발동</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
     <row r="47" ht="56" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>B6c</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 처치했을 때</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr"/>
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
     <row r="48" ht="56" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>B11a</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C48" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 체크당했을 때</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr"/>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>#지정불가 #비밀</t>
         </is>
       </c>
     </row>
     <row r="49" ht="56" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>B11b</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 내 턴 시작</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr"/>
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>아군 비숍이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>#비밀</t>
         </is>
       </c>
     </row>
     <row r="50" ht="56" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>B11c</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C50" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 예약 발동</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
     <row r="51" ht="56" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Q1a</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr"/>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr"/>
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>이동 직후</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr"/>
+      <c r="J51" s="12" t="inlineStr"/>
     </row>
     <row r="52" ht="56" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Q1b</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="H52" s="12" t="inlineStr"/>
+      <c r="I52" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>#지정불가</t>
         </is>
       </c>
     </row>
     <row r="53" ht="56" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>Q1c</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr"/>
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr"/>
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="54" ht="56" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Q3a</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C54" s="8" t="n">
+      <c r="C54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr"/>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr"/>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr"/>
+      <c r="I54" s="12" t="inlineStr">
         <is>
           <t>초기화</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J54" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="55" ht="56" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Q3b</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr"/>
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 수동 발동 가능 판정 / 수동 발동</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="H55" s="12" t="inlineStr"/>
+      <c r="I55" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>#포영</t>
         </is>
       </c>
     </row>
     <row r="56" ht="56" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Q3c</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C56" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr"/>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr"/>
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr"/>
+      <c r="J56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="56" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Q6a</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr"/>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J57" s="12" t="inlineStr">
         <is>
           <t>#포영</t>
         </is>
       </c>
     </row>
     <row r="58" ht="56" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Q6b</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C58" s="8" t="n">
+      <c r="C58" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr"/>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr"/>
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr"/>
+      <c r="J58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="56" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>Q6c</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C59" s="8" t="n">
+      <c r="C59" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr"/>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr"/>
+      <c r="I59" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J59" s="8" t="inlineStr">
+      <c r="J59" s="12" t="inlineStr">
         <is>
           <t>#교환</t>
         </is>
       </c>
     </row>
     <row r="60" ht="56" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>Q11a</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C60" s="8" t="n">
+      <c r="C60" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr"/>
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr"/>
+      <c r="I60" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J60" s="8" t="inlineStr">
+      <c r="J60" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="61" ht="56" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>Q11b</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C61" s="8" t="n">
+      <c r="C61" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr"/>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr"/>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 매 턴 지속</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="H61" s="12" t="inlineStr"/>
+      <c r="I61" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J61" s="12" t="inlineStr">
         <is>
           <t>#포영 #제거</t>
         </is>
       </c>
     </row>
     <row r="62" ht="56" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Q11c</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C62" s="8" t="n">
+      <c r="C62" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr"/>
+      <c r="I62" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다</t>
         </is>
       </c>
-      <c r="J62" s="8" t="inlineStr"/>
+      <c r="J62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="56" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>K1a</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr"/>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t>획득 즉시 / 체크당했을 때</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="H63" s="12" t="inlineStr"/>
+      <c r="I63" s="12" t="inlineStr">
         <is>
           <t>아군 퀸이 없습니다</t>
         </is>
       </c>
-      <c r="J63" s="8" t="inlineStr"/>
+      <c r="J63" s="12" t="inlineStr"/>
     </row>
     <row r="64" ht="56" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>K1b</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C64" s="8" t="n">
+      <c r="C64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr"/>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr"/>
+      <c r="I64" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr"/>
+      <c r="J64" s="12" t="inlineStr"/>
     </row>
     <row r="65" ht="56" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>K1c</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr"/>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr"/>
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>자신의 모든 제거를 처치로 간주합니다.</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>패시브 (엔진이 직접 처리)</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr"/>
+      <c r="I65" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J65" s="8" t="inlineStr">
+      <c r="J65" s="12" t="inlineStr">
         <is>
           <t>#제거</t>
         </is>
       </c>
     </row>
     <row r="66" ht="56" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>K1d</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>K3a</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C66" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="C66" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr"/>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67" ht="56" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>K3b</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr"/>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68" ht="56" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>K3c</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr"/>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69" ht="56" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>K6a</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr"/>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr"/>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70" ht="56" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>K6b</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr"/>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71" ht="56" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>K6c</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr"/>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72" ht="56" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>K11a</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr"/>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>획득 즉시 / 수동 발동 가능 판정 / 수동 발동</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>아군 폰이 없습니다</t>
+        </is>
+      </c>
+      <c r="J72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73" ht="56" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>K11b</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>이후 모든 강화에 필요한 처치 기물 수가 1 줄어듭니다. (1·3·6·11 → 0·2·5·10)</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr"/>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>패시브 (엔진이 직접 처리)</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr"/>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>(조건 있음)</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>K11c</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr"/>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>획득 즉시</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>더 받을 강화가 없습니다</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67" ht="56" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>K3a</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr"/>
+      <c r="I74" s="12" t="inlineStr">
         <is>
           <t>(조건 있음)</t>
         </is>
       </c>
-      <c r="J67" s="8" t="inlineStr"/>
-    </row>
-    <row r="68" ht="56" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>K3b</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J68" s="8" t="inlineStr"/>
-    </row>
-    <row r="69" ht="56" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>K3c</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr"/>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J69" s="8" t="inlineStr"/>
-    </row>
-    <row r="70" ht="56" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>K6a</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr"/>
-    </row>
-    <row r="71" ht="56" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>K6b</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="56" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>K6c</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73" ht="56" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>K11a</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시 / 수동 발동 가능 판정 / 수동 발동</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>아군 폰이 없습니다</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74" ht="56" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>K11b</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>영구지속</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>패시브 (엔진이 직접 처리)</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr"/>
-    </row>
-    <row r="75" ht="56" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>K11c</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>획득 즉시</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>(조건 있음)</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr">
+      <c r="J74" s="12" t="inlineStr">
         <is>
           <t>#변이</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J75"/>
+  <autoFilter ref="A1:J74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4568,88 +4517,88 @@
       </c>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
+      <c r="A4" s="12" t="n"/>
+      <c r="B4" s="12" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>한 줄 요약</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>증강 73종은 game/src/augments.js 안에 '훅' 으로 구현되어 있습니다. 게임 진행 중 특정 시점(획득·처치·이동·턴 시작 등)이 되면 해당 시점에 등록된 증강이 실행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>드래프트 방식</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>처치 카운트가 1·3·6·11 에 닿으면, 그 처치를 해낸 기물의 칸(기물×티어)에 있는 선택지 3개를 그대로 펼쳐 보여주고 그중 1개만 고릅니다. 원본 증강표가 칸마다 3개씩 두고 있는 구조를 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>잠금 조건</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>지금 발동해도 아무 일이 일어나지 않는 증강은 고를 수 없게 막고 빨간 ✕ 로 표시합니다. 기본 규칙은 '해당 기물이 판에 하나도 없으면 잠금' 이고, 그 밖의 개별 조건은 '잠금 조건' 칸에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>자동 발동 추적</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>증강 훅을 실행하기 전후로 판을 통째로 비교해, 바뀐 칸을 자동으로 찾아냅니다. 그래서 73종 전부에 따로 코드를 넣지 않아도 '어느 증강 때문에 무엇이 바뀌었는지' 를 화면에 표시할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>패시브 증강</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>이동 규칙 자체를 바꾸는 증강(예: 룩이 기물을 통과, 폰이 뒤로 이동)은 훅이 아니라 체스 엔진의 이동 생성기(engine.js)가 직접 읽습니다. 표에서 '패시브' 로 표시된 것들입니다.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>용어</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>지정불가 · 제거 · 교환 · 포영 · 변이 · 비밀 여섯 가지를 용어로 정의하고, 증강 문구 안의 용어와 카드 아래 #태그를 같은 색으로 칠합니다. '처치' 도 용어지만 거의 모든 증강에 나와서 태그로는 달지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>이 파일은 자동 생성</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>tools/build_impl_xlsx.py 가 augments.js 를 직접 읽어서 만듭니다. 코드를 고친 뒤 다시 돌리면 표도 같이 갱신됩니다.</t>
         </is>

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>[B3c] 적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)
+          <t>[B3c] 적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)
 ▸ 발동 시점: 처치했을 때 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -932,8 +932,8 @@
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>[N1c] 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)
-▸ 발동 시점: 처치했을 때
+          <t>[N1c] 다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)
+▸ 발동 시점: 획득 즉시 / 처치했을 때
 ▸ 잠금 조건: 아군 나이트가 없습니다 (기본 규칙)
 ▸ 용어: #제거</t>
         </is>
@@ -2510,18 +2510,18 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>영구지속</t>
+          <t>횟수제한</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>처치했을 때</t>
+          <t>획득 즉시 / 처치했을 때</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr"/>

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>[P1a] 다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.
+          <t>[P1a] 다음 상대턴 동안, 지정한 아군 폰 하나가 지정불가 상태가 됩니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 폰이 없습니다
@@ -659,7 +659,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>[P3a] 내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.
+          <t>[P3a] 내 다음 2턴 동안, 폰으로 적을 처치하면 처치 수가 2배로 쌓입니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
@@ -673,7 +673,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>[P11a] 모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)
+          <t>[P11a] 모든 폰이 한 번에 두 칸까지 움직이고 처치할 수 있습니다. (지나갈 칸에 기물이 있으면 통과하지 못합니다.)
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
@@ -683,7 +683,7 @@
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>[P1b] 다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)
+          <t>[P1b] 다음 1회, 폰이 두 칸 전진할 수 있습니다. (지나갈 칸과 도착할 칸이 모두 비어 있어야 합니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
@@ -697,14 +697,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>[P6b] 폰이 정면에 있는 적 기물도 처치할 수 있습니다.
+          <t>[P6b] 폰이 바로 앞에 있는 적 기물도 처치할 수 있습니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>[P11b] 내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.
+          <t>[P11b] 지정한 아군 폰이 내 다음 3턴 동안 퀸이 됩니다. 3턴이 지나면 그 기물은 제거됩니다.
 ▸ 발동 시점: 획득 즉시 / 효과 만료
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 폰이 없습니다
@@ -716,7 +716,7 @@
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>[P1c] 적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.
+          <t>[P1c] 폰이 적을 처치하면, 그 폰과 가장 가까운 상대 폰이 다음 상대턴 동안 함께 포영됩니다.
 ▸ 발동 시점: 처치했을 때
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)
 ▸ 용어: #포영</t>
@@ -724,14 +724,14 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>[P3c] 폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)
+          <t>[P3c] 폰이 적을 처치한 뒤 원래 자리로 되돌아올 수 있습니다. (고르지 않아도 됩니다.)
 ▸ 발동 시점: 처치했을 때
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>[P6c] 적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)
+          <t>[P6c] 폰이 적을 처치하면, 그 폰 앞 2칸 이내에 있는 적 기물 하나와 위치를 교환합니다. 그 기물의 점수가 폰보다 높다면 폰으로 변이시킵니다. (킹 제외)
 ▸ 발동 시점: 처치했을 때
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)
@@ -740,7 +740,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>[P11c] 폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.
+          <t>[P11c] 폰이 반대편 끝이 아니어도, 판의 어느 한쪽 끝(a·h파일 또는 1·8랭크)에 닿으면 원하는 기물로 바꿀 수 있습니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 폰이 없습니다 (기본 규칙)</t>
         </is>
@@ -761,7 +761,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>[R3a] 다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)
+          <t>[R3a] 다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치할 수는 없습니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -769,7 +769,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>[R6a] 다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)
+          <t>[R6a] 다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 상대에게 룩이 없습니다</t>
         </is>
@@ -786,7 +786,7 @@
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>[R1b] 즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)
+          <t>[R1b] 즉시, 룩이 선 가로줄과 세로줄 중 하나를 골라 그 룩에서 4칸 이내의 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 룩이 없습니다 (기본 규칙)
@@ -795,7 +795,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>[R3b] 다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.
+          <t>[R3b] 룩이 적을 처치하면, 그 기물과 같은 종류의 상대 기물이 모두 2턴 동안 포영됩니다.
 ▸ 발동 시점: 처치했을 때
 ▸ 잠금 조건: 아군 룩이 없습니다 (기본 규칙)
 ▸ 용어: #포영</t>
@@ -803,14 +803,14 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>[R6b] 다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)
+          <t>[R6b] 다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 상대에게 룩이 없습니다</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>[R11b] 게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)
+          <t>[R11b] 게임 내내 한 번도 움직이지 않은 아군 기물 하나를 골라 룩으로 만듭니다. (킹 제외)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -821,7 +821,7 @@
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>[R1c] 내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.
+          <t>[R1c] 룩이 적을 처치하면, 그 룩과 지정한 상대 기물 하나가 내 다음 2턴 동안 지정불가 상태가 됩니다.
 ▸ 발동 시점: 처치했을 때
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 룩이 없습니다 (기본 규칙)
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>[R6c] 지정한 아군 룩과 상대 폰의 위치를 교환합니다.
+          <t>[R6c] 지정한 아군 룩과 지정한 상대 폰의 위치를 교환합니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>[R11c] 룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)
+          <t>[R11c] 룩이 킹과 같은 가로줄에 있다면 언제든 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 룩이 없습니다</t>
         </is>
@@ -870,7 +870,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>[N3a] 다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.
+          <t>[N3a] 다음 2회, 나이트의 상·하·좌·우 중 한 방향에 아군 폰이 있으면 그 폰과 나이트의 위치를 바꿉니다.
 ▸ 발동 시점: 획득 즉시 / 수동 발동 가능 판정 / 수동 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -878,7 +878,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>[N6a] 나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)
+          <t>[N6a] 나이트가 지나간 칸에 있던 기물을 피아 구분 없이 2턴 동안 포영시킵니다. (킹 제외)
 ▸ 발동 시점: 이동 직후
 ▸ 잠금 조건: 아군 나이트가 없습니다 (기본 규칙)
 ▸ 용어: #포영</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>[N11a] 나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.
+          <t>[N11a] 나이트 증강을 2개 이상 가지고 있다면, 빈칸에 나이트 2개를 소환합니다. 소환된 나이트는 1턴 동안 지정불가입니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 나이트를 2회 이상 강화해야 합니다
@@ -898,7 +898,7 @@
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>[N1b] 적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.
+          <t>[N1b] 나이트가 적을 처치할 때마다, 그 나이트와 아군 비숍 하나의 위치를 교환합니다.
 ▸ 발동 시점: 처치했을 때
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -907,14 +907,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>[N3b] 다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)
+          <t>[N3b] 다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>[N6b] 상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)
+          <t>[N6b] 상대 나이트가 내 나이트와 가로·세로 모두 5칸 이상 떨어져 있다면 그 나이트를 처치합니다. (대상이 여럿이면 내가 고릅니다.)
 ▸ 발동 시점: 내 턴 시작
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -932,7 +932,7 @@
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>[N1c] 다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)
+          <t>[N1c] 다음 1회, 나이트가 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)
 ▸ 발동 시점: 획득 즉시 / 처치했을 때
 ▸ 잠금 조건: 아군 나이트가 없습니다 (기본 규칙)
 ▸ 용어: #제거</t>
@@ -940,7 +940,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>[N3c] 지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.
+          <t>[N3c] 지정한 아군 나이트의 좌우 한 칸에 모두 적 기물이 있고 둘 다 나이트보다 점수가 높다면, 나이트가 둘 중 점수가 낮은 기물로 변이합니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -949,7 +949,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>[N6c] 즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)
+          <t>[N6c] 즉시, 나이트가 상대의 가장 낮은 점수 기물 하나를 없애고 그 자리로 이동합니다. (킹·퀸 제외. 대상이 여럿이면 내가 고릅니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -957,7 +957,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>[N11c] 자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.
+          <t>[N11c] 아군 나이트와 상대 퀸이 모두 살아 있다면, 둘 다 제거합니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -973,7 +973,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>[B1a] 다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.
+          <t>[B1a] 다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 두 폰의 위치를 교환합니다.
 ▸ 발동 시점: 획득 즉시 / 내 턴 시작
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -982,7 +982,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>[B3a] 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.
+          <t>[B3a] 1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 홀수라면 아군 진영 빈칸에 폰 하나를 소환합니다.
 ▸ 발동 시점: 처치했을 때 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
@@ -991,15 +991,15 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>[B6a] 상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)
+          <t>[B6a] 상대의 다음 2턴 동안, 비숍이 처치당하면 그 비숍을 처치한 상대 기물도 함께 제거됩니다. (킹·퀸 제외)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
-▸ 용어: #비밀</t>
+▸ 용어: #제거 #비밀</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>[B11a] 다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.
+          <t>[B11a] 다음 1회, 아군 킹이 체크를 당하면 체크를 건 기물을 1턴 동안 지정불가 상태로 만듭니다.
 ▸ 발동 시점: 획득 즉시 / 체크당했을 때
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
 ▸ 용어: #지정불가 #비밀</t>
@@ -1010,7 +1010,7 @@
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>[B1b] 내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)
+          <t>[B1b] 내 다음 2턴 동안 비숍이 움직이지 못합니다. 그동안 비숍에 인접한 칸 중 비숍이 선 칸과 같은 색인 칸으로 적 기물이 오면 그 기물을 제거합니다. (킹 제외)
 ▸ 발동 시점: 획득 즉시 / 상대가 둔 직후
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
 ▸ 용어: #제거 #비밀</t>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>[B3b] 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.
+          <t>[B3b] 1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 짝수라면 아군 진영 빈칸에 폰 하나를 소환합니다.
 ▸ 발동 시점: 처치했을 때 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>[B6b] 상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)
+          <t>[B6b] 상대의 다음 1턴 동안 지정한 상대 기물이 움직이지 않으면, 그 기물을 제거합니다. (킹·퀸 제외)
 ▸ 발동 시점: 획득 즉시 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>[B11b] 아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.
+          <t>[B11b] 아군 퀸이 잡힌 상태라면, 내 다음 3턴 동안 비숍이 퀸처럼 움직일 수 있습니다.
 ▸ 발동 시점: 획득 즉시 / 내 턴 시작
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
 ▸ 용어: #비밀</t>
@@ -1047,7 +1047,7 @@
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>[B1c] 다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.
+          <t>[B1c] 지정한 상대 폰이 상대의 다음 2턴 동안 한 번도 움직이지 않으면, 그 폰을 제거합니다.
 ▸ 발동 시점: 획득 즉시 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 상대 폰이 없습니다
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>[B3c] 적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)
+          <t>[B3c] 비숍이 적을 처치하고 2턴을 살아남으면, 잃었던 아군 기물 하나를 그 기물의 시작 칸에 되살립니다. (그 칸이 비어 있어야 합니다.)
 ▸ 발동 시점: 처치했을 때 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>[B6c] 다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)
+          <t>[B6c] 다음 1회, 비숍이 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)
 ▸ 발동 시점: 획득 즉시 / 처치했을 때
 ▸ 잠금 조건: 아군 비숍이 없습니다 (기본 규칙)
 ▸ 용어: #제거 #비밀</t>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>[B11c] 지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.
+          <t>[B11c] 지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않으면, 그 기물이 받고 있던 증강 효과가 모두 사라집니다.
 ▸ 발동 시점: 획득 즉시 / 예약 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)
@@ -1089,14 +1089,14 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>[Q1a] 아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.
+          <t>[Q1a] 아군 퀸이 판의 긴 대각선(a1–h8 / a8–h1) 칸에 도착하면, 다음 턴에 그 대각선 위의 빈칸 한 곳으로 순간이동할 수 있습니다.
 ▸ 발동 시점: 이동 직후
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>[Q3a] 자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)
+          <t>[Q3a] 나와 상대가 지금까지 얻은 증강 효과를 모두 제거합니다. (이 증강도 함께 사라지며, 이후 얻는 증강은 정상 적용됩니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 초기화
 ▸ 용어: #제거</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>[Q6a] 다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)
+          <t>[Q6a] 다음 상대턴 동안, 아군 퀸과 지정한 기물 하나를 함께 포영시킵니다. (킹 제외)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>[Q11a] 퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)
+          <t>[Q11a] 퀸 주변 한 칸의 모든 기물과, 그 기물들과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)
 ▸ 용어: #제거</t>
@@ -1124,7 +1124,7 @@
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>[Q1b] 내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.
+          <t>[Q1b] 내 다음 5턴 동안, 아군 퀸과 상대 퀸이 함께 지정불가 상태가 됩니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)
 ▸ 용어: #지정불가</t>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>[Q3b] 다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.
+          <t>[Q3b] 1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.
 ▸ 발동 시점: 획득 즉시 / 수동 발동 가능 판정 / 수동 발동
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)
 ▸ 용어: #포영</t>
@@ -1140,14 +1140,14 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>[Q6b] 퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.
+          <t>[Q6b] 퀸 증강을 1개 이상 가지고 있다면, 퀸이 나이트처럼도 움직일 수 있습니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>[Q11b] 아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)
+          <t>[Q11b] 아군 퀸이 2턴 동안 포영되며, 그동안 포영된 자리에서 두 칸 이내에 들어온 상대 기물을 제거합니다. (킹 제외)
 ▸ 발동 시점: 획득 즉시 / 매 턴 지속
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)
 ▸ 용어: #포영 #제거</t>
@@ -1158,7 +1158,7 @@
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>[Q1c] 아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)
+          <t>[Q1c] 아군 퀸과 상대 퀸을 함께 제거합니다. (양쪽 퀸이 모두 살아 있을 때만 고를 수 있습니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)
 ▸ 용어: #제거</t>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>[Q3c] 이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.
+          <t>[Q3c] 이 판에서 아군 퀸이 처치당해도 상대의 처치 수에 더해지지 않습니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>[Q6c] 아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.
+          <t>[Q6c] 아군 퀸과, 킹을 제외한 상대의 가장 높은 점수 기물의 위치를 교환합니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)
 ▸ 용어: #교환</t>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>[Q11c] 퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.
+          <t>[Q11c] 퀸이 어디에 있든 아군 킹 주변 한 칸의 빈칸으로 움직일 수 있습니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: 아군 퀸이 없습니다</t>
         </is>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>[K1a] 다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.
+          <t>[K1a] 다음 1회, 킹이 체크를 당하면 퀸과 킹의 위치를 바꿀 수 있습니다.
 ▸ 발동 시점: 획득 즉시 / 체크당했을 때
 ▸ 잠금 조건: 아군 퀸이 없습니다</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>[K3a] 나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.
+          <t>[K3a] 나이트·비숍 중 한 기물의 6개 티어 증강 하나를 골라 추가로 얻습니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>[K6a] 다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.
+          <t>[K6a] 다음 1회, 다른 기물을 움직인 뒤 킹도 한 번 더 움직일 수 있습니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>[K11a] 킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)
+          <t>[K11a] 킹이 아군 폰 하나를 위아래 방향으로 지정한 칸까지 옮깁니다. (다른 기물을 넘어갈 수는 없습니다.)
 ▸ 발동 시점: 획득 즉시 / 수동 발동 가능 판정 / 수동 발동
 ▸ 대상 지정 필요
 ▸ 잠금 조건: 아군 폰이 없습니다</t>
@@ -1228,14 +1228,14 @@
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>[K1b] 자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.
+          <t>[K1b] 다음 증강을 고를 때 선택지를 두 개 고를 수 있습니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>[K3b] 상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)
+          <t>[K3b] 상대와 나의 기물 점수 차이만큼 예산을 받아, 그만큼 원하는 기물을 킹의 상하좌우 빈칸에 배치합니다. (폰 1 · 나이트 3 · 비숍 3 · 룩 5 · 퀸 9점. 이미 기물이 있는 칸에는 배치할 수 없습니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>[K6b] 지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.
+          <t>[K6b] 같은 기물의 증강을 2개 이상 가지고 있다면, 그 기물의 1개 티어 증강 하나를 추가로 얻습니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>[K11b] 이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.
+          <t>[K11b] 이 증강을 얻은 뒤부터, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 차지하면 즉시 승리합니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: (조건 있음)</t>
         </is>
@@ -1261,7 +1261,7 @@
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>[K1c] 자신의 모든 제거를 처치로 간주합니다.
+          <t>[K1c] 내가 일으킨 제거를 모두 처치로 셉니다.
 ▸ 발동 시점: 패시브 (엔진이 직접 처리)
 ▸ 잠금 조건: (조건 있음)
 ▸ 용어: #제거</t>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>[K3c] 룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.
+          <t>[K3c] 룩·퀸 중 한 기물의 11개 티어 증강 하나를 골라 추가로 얻습니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>[K6c] 이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.
+          <t>[K6c] 이미 가진 증강 하나를 골라, 같은 기물·같은 티어의 다른 증강으로 바꿉니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 대상 지정 필요
 ▸ 잠금 조건: (조건 있음)</t>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>[K11c] 서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.
+          <t>[K11c] 양쪽 킹을 제외한 모든 기물을 폰으로 변이시킵니다.
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: (조건 있음)
 ▸ 용어: #변이</t>
@@ -1444,7 +1444,7 @@
       <c r="E3" s="12" t="inlineStr"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.</t>
+          <t>다음 상대턴 동안, 지정한 아군 폰 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
@@ -1490,7 +1490,7 @@
       <c r="E4" s="12" t="inlineStr"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)</t>
+          <t>다음 1회, 폰이 두 칸 전진할 수 있습니다. (지나갈 칸과 도착할 칸이 모두 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
@@ -1528,7 +1528,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.</t>
+          <t>폰이 적을 처치하면, 그 폰과 가장 가까운 상대 폰이 다음 상대턴 동안 함께 포영됩니다.</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -1570,7 +1570,7 @@
       <c r="E6" s="12" t="inlineStr"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.</t>
+          <t>내 다음 2턴 동안, 폰으로 적을 처치하면 처치 수가 2배로 쌓입니다.</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)</t>
+          <t>폰이 적을 처치한 뒤 원래 자리로 되돌아올 수 있습니다. (고르지 않아도 됩니다.)</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -1722,7 +1722,7 @@
       <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>폰이 정면에 있는 적 기물도 처치할 수 있습니다.</t>
+          <t>폰이 바로 앞에 있는 적 기물도 처치할 수 있습니다.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -1760,7 +1760,7 @@
       <c r="E11" s="12" t="inlineStr"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
+          <t>폰이 적을 처치하면, 그 폰 앞 2칸 이내에 있는 적 기물 하나와 위치를 교환합니다. 그 기물의 점수가 폰보다 높다면 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1806,7 +1806,7 @@
       <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
+          <t>모든 폰이 한 번에 두 칸까지 움직이고 처치할 수 있습니다. (지나갈 칸에 기물이 있으면 통과하지 못합니다.)</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       <c r="E13" s="12" t="inlineStr"/>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.</t>
+          <t>지정한 아군 폰이 내 다음 3턴 동안 퀸이 됩니다. 3턴이 지나면 그 기물은 제거됩니다.</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
+          <t>폰이 반대편 끝이 아니어도, 판의 어느 한쪽 끝(a·h파일 또는 1·8랭크)에 닿으면 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -1966,7 +1966,7 @@
       <c r="E16" s="12" t="inlineStr"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
+          <t>즉시, 룩이 선 가로줄과 세로줄 중 하나를 골라 그 룩에서 4칸 이내의 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -2012,7 +2012,7 @@
       <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.</t>
+          <t>룩이 적을 처치하면, 그 룩과 지정한 상대 기물 하나가 내 다음 2턴 동안 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -2058,7 +2058,7 @@
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)</t>
+          <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치할 수는 없습니다.)</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -2100,7 +2100,7 @@
       <c r="E19" s="12" t="inlineStr"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.</t>
+          <t>룩이 적을 처치하면, 그 기물과 같은 종류의 상대 기물이 모두 2턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -2184,7 +2184,7 @@
       <c r="E21" s="12" t="inlineStr"/>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -2222,7 +2222,7 @@
       <c r="E22" s="12" t="inlineStr"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2260,7 +2260,7 @@
       <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>지정한 아군 룩과 상대 폰의 위치를 교환합니다.</t>
+          <t>지정한 아군 룩과 지정한 상대 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -2344,7 +2344,7 @@
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
+          <t>게임 내내 한 번도 움직이지 않은 아군 기물 하나를 골라 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
+          <t>룩이 킹과 같은 가로줄에 있다면 언제든 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -2470,7 +2470,7 @@
       <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.</t>
+          <t>나이트가 적을 처치할 때마다, 그 나이트와 아군 비숍 하나의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -2516,7 +2516,7 @@
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 나이트가 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -2558,7 +2558,7 @@
       <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
+          <t>다음 2회, 나이트의 상·하·좌·우 중 한 방향에 아군 폰이 있으면 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -2600,7 +2600,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
+          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -2638,7 +2638,7 @@
       <c r="E32" s="12" t="inlineStr"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
+          <t>지정한 아군 나이트의 좌우 한 칸에 모두 적 기물이 있고 둘 다 나이트보다 점수가 높다면, 나이트가 둘 중 점수가 낮은 기물로 변이합니다.</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -2684,7 +2684,7 @@
       <c r="E33" s="12" t="inlineStr"/>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
+          <t>나이트가 지나간 칸에 있던 기물을 피아 구분 없이 2턴 동안 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="E34" s="12" t="inlineStr"/>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)</t>
+          <t>상대 나이트가 내 나이트와 가로·세로 모두 5칸 이상 떨어져 있다면 그 나이트를 처치합니다. (대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -2768,7 +2768,7 @@
       <c r="E35" s="12" t="inlineStr"/>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)</t>
+          <t>즉시, 나이트가 상대의 가장 낮은 점수 기물 하나를 없애고 그 자리로 이동합니다. (킹·퀸 제외. 대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="E36" s="12" t="inlineStr"/>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.</t>
+          <t>나이트 증강을 2개 이상 가지고 있다면, 빈칸에 나이트 2개를 소환합니다. 소환된 나이트는 1턴 동안 지정불가입니다.</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="E38" s="12" t="inlineStr"/>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.</t>
+          <t>아군 나이트와 상대 퀸이 모두 살아 있다면, 둘 다 제거합니다.</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
+          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 두 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
+          <t>내 다음 2턴 동안 비숍이 움직이지 못합니다. 그동안 비숍에 인접한 칸 중 비숍이 선 칸과 같은 색인 칸으로 적 기물이 오면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
+          <t>지정한 상대 폰이 상대의 다음 2턴 동안 한 번도 움직이지 않으면, 그 폰을 제거합니다.</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 홀수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 짝수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+          <t>비숍이 적을 처치하고 2턴을 살아남으면, 잃었던 아군 기물 하나를 그 기물의 시작 칸에 되살립니다. (그 칸이 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)</t>
+          <t>상대의 다음 2턴 동안, 비숍이 처치당하면 그 비숍을 처치한 상대 기물도 함께 제거됩니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>#비밀</t>
+          <t>#제거 #비밀</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)</t>
+          <t>상대의 다음 1턴 동안 지정한 상대 기물이 움직이지 않으면, 그 기물을 제거합니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
+          <t>다음 1회, 비숍이 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
+          <t>다음 1회, 아군 킹이 체크를 당하면 체크를 건 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.</t>
+          <t>아군 퀸이 잡힌 상태라면, 내 다음 3턴 동안 비숍이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
+          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않으면, 그 기물이 받고 있던 증강 효과가 모두 사라집니다.</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -3520,7 +3520,7 @@
       <c r="E51" s="12" t="inlineStr"/>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
+          <t>아군 퀸이 판의 긴 대각선(a1–h8 / a8–h1) 칸에 도착하면, 다음 턴에 그 대각선 위의 빈칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -3558,7 +3558,7 @@
       <c r="E52" s="12" t="inlineStr"/>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.</t>
+          <t>내 다음 5턴 동안, 아군 퀸과 상대 퀸이 함께 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -3600,7 +3600,7 @@
       <c r="E53" s="12" t="inlineStr"/>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
+          <t>아군 퀸과 상대 퀸을 함께 제거합니다. (양쪽 퀸이 모두 살아 있을 때만 고를 수 있습니다.)</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -3642,7 +3642,7 @@
       <c r="E54" s="12" t="inlineStr"/>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
+          <t>나와 상대가 지금까지 얻은 증강 효과를 모두 제거합니다. (이 증강도 함께 사라지며, 이후 얻는 증강은 정상 적용됩니다.)</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -3684,7 +3684,7 @@
       <c r="E55" s="12" t="inlineStr"/>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.</t>
+          <t>1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -3726,7 +3726,7 @@
       <c r="E56" s="12" t="inlineStr"/>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.</t>
+          <t>이 판에서 아군 퀸이 처치당해도 상대의 처치 수에 더해지지 않습니다.</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -3764,7 +3764,7 @@
       <c r="E57" s="12" t="inlineStr"/>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
+          <t>다음 상대턴 동안, 아군 퀸과 지정한 기물 하나를 함께 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="E58" s="12" t="inlineStr"/>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
+          <t>퀸 증강을 1개 이상 가지고 있다면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -3848,7 +3848,7 @@
       <c r="E59" s="12" t="inlineStr"/>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.</t>
+          <t>아군 퀸과, 킹을 제외한 상대의 가장 높은 점수 기물의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="E60" s="12" t="inlineStr"/>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
+          <t>퀸 주변 한 칸의 모든 기물과, 그 기물들과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -3932,7 +3932,7 @@
       <c r="E61" s="12" t="inlineStr"/>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
+          <t>아군 퀸이 2턴 동안 포영되며, 그동안 포영된 자리에서 두 칸 이내에 들어온 상대 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -3974,7 +3974,7 @@
       <c r="E62" s="12" t="inlineStr"/>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
+          <t>퀸이 어디에 있든 아군 킹 주변 한 칸의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -4012,7 +4012,7 @@
       <c r="E63" s="12" t="inlineStr"/>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
+          <t>다음 1회, 킹이 체크를 당하면 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -4050,7 +4050,7 @@
       <c r="E64" s="12" t="inlineStr"/>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.</t>
+          <t>다음 증강을 고를 때 선택지를 두 개 고를 수 있습니다.</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -4088,7 +4088,7 @@
       <c r="E65" s="12" t="inlineStr"/>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>자신의 모든 제거를 처치로 간주합니다.</t>
+          <t>내가 일으킨 제거를 모두 처치로 셉니다.</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="E66" s="12" t="inlineStr"/>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>나이트·비숍 중 한 기물의 6개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -4172,7 +4172,7 @@
       <c r="E67" s="12" t="inlineStr"/>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
+          <t>상대와 나의 기물 점수 차이만큼 예산을 받아, 그만큼 원하는 기물을 킹의 상하좌우 빈칸에 배치합니다. (폰 1 · 나이트 3 · 비숍 3 · 룩 5 · 퀸 9점. 이미 기물이 있는 칸에는 배치할 수 없습니다.)</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -4214,7 +4214,7 @@
       <c r="E68" s="12" t="inlineStr"/>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>룩·퀸 중 한 기물의 11개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -4256,7 +4256,7 @@
       <c r="E69" s="12" t="inlineStr"/>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
+          <t>다음 1회, 다른 기물을 움직인 뒤 킹도 한 번 더 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       <c r="E70" s="12" t="inlineStr"/>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>같은 기물의 증강을 2개 이상 가지고 있다면, 그 기물의 1개 티어 증강 하나를 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       <c r="E71" s="12" t="inlineStr"/>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+          <t>이미 가진 증강 하나를 골라, 같은 기물·같은 티어의 다른 증강으로 바꿉니다.</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -4378,7 +4378,7 @@
       <c r="E72" s="12" t="inlineStr"/>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
+          <t>킹이 아군 폰 하나를 위아래 방향으로 지정한 칸까지 옮깁니다. (다른 기물을 넘어갈 수는 없습니다.)</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="E73" s="12" t="inlineStr"/>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+          <t>이 증강을 얻은 뒤부터, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 차지하면 즉시 승리합니다.</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -4458,7 +4458,7 @@
       <c r="E74" s="12" t="inlineStr"/>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
+          <t>양쪽 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -1132,8 +1132,8 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>[Q3b] 1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.
-▸ 발동 시점: 획득 즉시 / 수동 발동 가능 판정 / 수동 발동
+          <t>[Q3b] 증강을 얻는 즉시, 아군 퀸이 다음 상대턴 동안 포영됩니다.
+▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 퀸이 없습니다 (기본 규칙)
 ▸ 용어: #포영</t>
         </is>
@@ -3684,12 +3684,12 @@
       <c r="E55" s="12" t="inlineStr"/>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
+          <t>증강을 얻는 즉시, 아군 퀸이 다음 상대턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>획득 즉시 / 수동 발동 가능 판정 / 수동 발동</t>
+          <t>획득 즉시</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr"/>

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>[N3b] 다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)
+          <t>[N3b] 양쪽이 한 턴씩 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)
 ▸ 발동 시점: 획득 즉시
 ▸ 잠금 조건: 아군 나이트가 없습니다 (기본 규칙)</t>
         </is>
@@ -2600,7 +2600,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
+          <t>양쪽이 한 턴씩 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">

--- a/docs/무제체스_증강_구현표.xlsx
+++ b/docs/무제체스_증강_구현표.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구현 격자" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구현 목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구조 설명" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어 색상" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="구현 격자" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="구현 목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="구조 설명" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="용어 색상" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구현 목록'!$A$1:$J$74</definedName>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>증강 73종은 game/src/augments.js 안에 '훅' 으로 구현되어 있습니다. 게임 진행 중 특정 시점(획득·처치·이동·턴 시작 등)이 되면 해당 시점에 등록된 증강이 실행됩니다.</t>
+          <t>증강 72종은 game/src/augments.js 안에 '훅' 으로 구현되어 있습니다. 게임 진행 중 특정 시점(획득·처치·이동·턴 시작 등)이 되면 해당 시점에 등록된 증강이 실행됩니다.</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>증강 훅을 실행하기 전후로 판을 통째로 비교해, 바뀐 칸을 자동으로 찾아냅니다. 그래서 73종 전부에 따로 코드를 넣지 않아도 '어느 증강 때문에 무엇이 바뀌었는지' 를 화면에 표시할 수 있습니다.</t>
+          <t>증강 훅을 실행하기 전후로 판을 통째로 비교해, 바뀐 칸을 자동으로 찾아냅니다. 그래서 72종 전부에 따로 코드를 넣지 않아도 '어느 증강 때문에 무엇이 바뀌었는지' 를 화면에 표시할 수 있습니다.</t>
         </is>
       </c>
     </row>
